--- a/output/Majlas_CBA.xlsx
+++ b/output/Majlas_CBA.xlsx
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>50000000</v>
+        <v>75000000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/output/Majlas_CBA.xlsx
+++ b/output/Majlas_CBA.xlsx
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>0.025</v>
+        <v>0.042</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
